--- a/data/trans_dic/P2B_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2B_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales</t>
+          <t>Hogares con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,18; 26,9</t>
+          <t>17,59; 26,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44,95; 56,58</t>
+          <t>43,83; 55,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35,17; 47,24</t>
+          <t>35,71; 47,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,24; 23,89</t>
+          <t>14,49; 23,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21,91; 33,78</t>
+          <t>22,06; 33,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,51; 63,87</t>
+          <t>51,11; 63,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,4; 57,58</t>
+          <t>44,81; 57,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,37; 26,56</t>
+          <t>18,69; 26,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,47; 27,45</t>
+          <t>20,89; 28,15</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49,27; 57,86</t>
+          <t>48,77; 57,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41,71; 50,79</t>
+          <t>42,02; 50,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,7; 23,41</t>
+          <t>17,71; 23,46</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,38; 28,11</t>
+          <t>16,89; 27,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>43,59; 55,46</t>
+          <t>43,88; 55,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40,85; 53,19</t>
+          <t>40,74; 52,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,72; 24,8</t>
+          <t>15,48; 24,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,46; 35,82</t>
+          <t>24,99; 35,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>57,41; 69,06</t>
+          <t>56,59; 68,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,66; 61,92</t>
+          <t>50,28; 61,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,93; 28,53</t>
+          <t>20,36; 28,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,17; 30,0</t>
+          <t>22,76; 30,53</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51,69; 59,73</t>
+          <t>51,47; 60,23</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47,37; 55,89</t>
+          <t>47,63; 55,64</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,91; 25,39</t>
+          <t>19,25; 25,46</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,08; 26,93</t>
+          <t>19,15; 27,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46,71; 55,83</t>
+          <t>46,8; 55,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,94; 47,74</t>
+          <t>38,02; 47,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,77; 32,12</t>
+          <t>22,47; 31,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,39; 37,33</t>
+          <t>21,99; 36,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,71; 60,36</t>
+          <t>46,76; 60,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,19; 53,63</t>
+          <t>35,73; 52,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,71; 30,16</t>
+          <t>18,7; 30,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,03; 28,36</t>
+          <t>21,17; 28,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48,44; 55,97</t>
+          <t>48,0; 55,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39,13; 47,62</t>
+          <t>38,76; 47,39</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,86; 30,55</t>
+          <t>22,65; 30,34</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,48; 24,48</t>
+          <t>19,42; 24,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51,18; 57,73</t>
+          <t>51,25; 57,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,25; 42,83</t>
+          <t>36,21; 42,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,06; 28,63</t>
+          <t>22,01; 28,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,87; 29,75</t>
+          <t>22,69; 29,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,04; 65,41</t>
+          <t>57,2; 64,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,65; 57,66</t>
+          <t>49,69; 57,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,17; 74,62</t>
+          <t>22,17; 72,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,42; 25,77</t>
+          <t>21,55; 25,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54,77; 59,52</t>
+          <t>54,63; 59,77</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42,87; 48,18</t>
+          <t>43,28; 48,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,37; 57,94</t>
+          <t>23,52; 60,18</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,76; 27,44</t>
+          <t>17,2; 27,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>47,0; 56,51</t>
+          <t>47,04; 57,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38,86; 47,84</t>
+          <t>38,68; 47,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,13; 26,0</t>
+          <t>17,31; 26,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,78; 29,77</t>
+          <t>21,72; 29,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,3; 60,77</t>
+          <t>53,24; 61,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,38; 50,13</t>
+          <t>42,36; 50,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,42; 30,69</t>
+          <t>19,32; 31,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,57; 28,09</t>
+          <t>21,67; 27,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52,32; 58,2</t>
+          <t>51,95; 58,13</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42,0; 47,92</t>
+          <t>41,91; 48,01</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,77; 27,58</t>
+          <t>18,25; 27,85</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,52; 23,85</t>
+          <t>11,26; 23,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>39,05; 55,31</t>
+          <t>39,04; 55,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,69; 45,51</t>
+          <t>30,39; 45,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,77; 28,93</t>
+          <t>9,39; 31,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,15; 27,3</t>
+          <t>21,95; 27,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>41,04; 47,27</t>
+          <t>40,74; 47,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,09; 41,81</t>
+          <t>34,96; 41,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30,65; 37,44</t>
+          <t>30,22; 37,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21,44; 26,35</t>
+          <t>21,46; 26,27</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>41,57; 47,53</t>
+          <t>41,63; 47,68</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>35,26; 41,36</t>
+          <t>35,06; 41,62</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>27,98; 34,57</t>
+          <t>28,16; 34,93</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>20,15; 23,7</t>
+          <t>20,37; 23,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>49,84; 53,71</t>
+          <t>50,14; 53,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39,54; 43,56</t>
+          <t>39,74; 43,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20,87; 24,56</t>
+          <t>21,03; 24,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,57; 27,88</t>
+          <t>24,53; 27,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,28; 55,97</t>
+          <t>52,23; 55,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,15; 48,91</t>
+          <t>45,02; 48,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25,62; 47,89</t>
+          <t>25,74; 47,79</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,88; 25,27</t>
+          <t>23,0; 25,32</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51,75; 54,46</t>
+          <t>51,8; 54,41</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43,21; 45,84</t>
+          <t>43,09; 45,91</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>24,15; 38,49</t>
+          <t>24,25; 39,98</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales</t>
+          <t>Hogares con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>65885; 97496</t>
+          <t>63776; 97276</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>152656; 192140</t>
+          <t>148859; 189246</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>101584; 136468</t>
+          <t>103162; 136601</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53615; 84059</t>
+          <t>50967; 82371</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>54662; 84267</t>
+          <t>55033; 82627</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>132619; 167689</t>
+          <t>134189; 167372</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>124421; 157803</t>
+          <t>122826; 157272</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>59633; 86211</t>
+          <t>60655; 86884</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>125259; 168004</t>
+          <t>127833; 172274</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>296712; 348410</t>
+          <t>293661; 346494</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>234794; 285913</t>
+          <t>236532; 283141</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>119703; 158323</t>
+          <t>119765; 158678</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>46255; 74822</t>
+          <t>44951; 72910</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>153427; 195199</t>
+          <t>154431; 194850</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>115498; 150368</t>
+          <t>115170; 148135</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>45382; 71580</t>
+          <t>44690; 71837</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>75157; 105743</t>
+          <t>73771; 105064</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>172802; 207872</t>
+          <t>170332; 204737</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>154156; 188409</t>
+          <t>152993; 188082</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>55951; 80099</t>
+          <t>57170; 78604</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>124475; 168438</t>
+          <t>127788; 171427</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>337508; 390012</t>
+          <t>336073; 393241</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>278053; 328062</t>
+          <t>279614; 326584</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>107687; 144576</t>
+          <t>109620; 144994</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>82863; 116943</t>
+          <t>83188; 119043</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>244824; 292664</t>
+          <t>245288; 289570</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>160255; 201644</t>
+          <t>160606; 201101</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>70521; 99481</t>
+          <t>69586; 98440</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>33846; 56443</t>
+          <t>33252; 55710</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>109504; 141504</t>
+          <t>109629; 141444</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>54210; 80321</t>
+          <t>53510; 79169</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25097; 40461</t>
+          <t>25095; 40643</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>123155; 166083</t>
+          <t>123946; 166303</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>367462; 424595</t>
+          <t>364105; 420530</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>223879; 272502</t>
+          <t>221776; 271149</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>101446; 135615</t>
+          <t>100554; 134654</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>191592; 240749</t>
+          <t>190993; 244084</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>491797; 554707</t>
+          <t>492421; 556242</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>316390; 373875</t>
+          <t>316048; 374043</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>156083; 202579</t>
+          <t>155781; 202139</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>137569; 178917</t>
+          <t>136457; 178936</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>375819; 430969</t>
+          <t>376863; 426904</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>325688; 378272</t>
+          <t>325993; 376115</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>175313; 590035</t>
+          <t>175271; 573029</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>339444; 408481</t>
+          <t>341532; 405412</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>887191; 964084</t>
+          <t>884887; 968168</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>655449; 736561</t>
+          <t>661752; 739404</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>350224; 868149</t>
+          <t>352371; 901720</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>47785; 73852</t>
+          <t>46295; 73063</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>194690; 234121</t>
+          <t>194853; 237400</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>186801; 229977</t>
+          <t>185922; 230612</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>58692; 89077</t>
+          <t>59315; 89189</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>109382; 149499</t>
+          <t>109033; 150163</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>374767; 427275</t>
+          <t>374349; 430794</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>279465; 330575</t>
+          <t>279367; 331095</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>130169; 216895</t>
+          <t>136563; 220542</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>166345; 216619</t>
+          <t>167099; 214448</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>584627; 650333</t>
+          <t>580451; 649567</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>478892; 546330</t>
+          <t>477833; 547412</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>207480; 289486</t>
+          <t>191508; 292266</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16717; 34613</t>
+          <t>16343; 34548</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>59893; 84836</t>
+          <t>59881; 84663</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>44625; 68411</t>
+          <t>45684; 68812</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9334; 30787</t>
+          <t>9989; 33177</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>237677; 292863</t>
+          <t>235561; 292995</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>400349; 461076</t>
+          <t>397350; 466279</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>315675; 376063</t>
+          <t>314456; 373982</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>178723; 218376</t>
+          <t>176264; 215990</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>261136; 320927</t>
+          <t>261349; 319948</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>469279; 536544</t>
+          <t>469916; 538239</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>370189; 434184</t>
+          <t>368014; 436927</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>192941; 238380</t>
+          <t>194168; 240897</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>495698; 583275</t>
+          <t>501252; 583018</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1367898; 1474059</t>
+          <t>1375936; 1479626</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>987630; 1087944</t>
+          <t>992598; 1093651</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>439644; 517524</t>
+          <t>443163; 515755</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>705637; 800830</t>
+          <t>704477; 799555</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1639148; 1754837</t>
+          <t>1637716; 1754669</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1328847; 1439571</t>
+          <t>1324977; 1435480</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>722636; 1350532</t>
+          <t>725908; 1347730</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1219949; 1347438</t>
+          <t>1226400; 1350393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3042465; 3202261</t>
+          <t>3045600; 3199012</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2350846; 2494054</t>
+          <t>2344664; 2497812</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1189927; 1896268</t>
+          <t>1194835; 1969747</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2B_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2B_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,59; 26,84</t>
+          <t>17,92; 27,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>43,83; 55,72</t>
+          <t>44,69; 55,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35,71; 47,29</t>
+          <t>35,3; 47,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,49; 23,41</t>
+          <t>15,81; 24,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,06; 33,12</t>
+          <t>21,54; 32,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,11; 63,75</t>
+          <t>50,44; 63,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,81; 57,38</t>
+          <t>45,4; 58,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,69; 26,77</t>
+          <t>18,74; 26,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,89; 28,15</t>
+          <t>20,61; 27,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48,77; 57,54</t>
+          <t>49,4; 57,61</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42,02; 50,3</t>
+          <t>41,91; 50,53</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,71; 23,46</t>
+          <t>18,37; 24,42</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,79%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,89; 27,39</t>
+          <t>17,22; 28,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>43,88; 55,36</t>
+          <t>43,45; 54,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40,74; 52,4</t>
+          <t>39,92; 52,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,48; 24,88</t>
+          <t>16,57; 26,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,99; 35,59</t>
+          <t>25,12; 35,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,59; 68,02</t>
+          <t>56,92; 68,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,28; 61,81</t>
+          <t>50,52; 61,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,36; 28,0</t>
+          <t>20,7; 29,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,76; 30,53</t>
+          <t>22,46; 29,82</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51,47; 60,23</t>
+          <t>51,43; 59,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47,63; 55,64</t>
+          <t>47,69; 56,15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,25; 25,46</t>
+          <t>19,72; 26,14</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,15; 27,41</t>
+          <t>18,71; 26,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46,8; 55,24</t>
+          <t>46,73; 55,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,02; 47,61</t>
+          <t>38,1; 47,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,47; 31,79</t>
+          <t>23,61; 33,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,99; 36,85</t>
+          <t>21,43; 37,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,76; 60,33</t>
+          <t>46,61; 60,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,73; 52,86</t>
+          <t>34,55; 52,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,7; 30,29</t>
+          <t>18,27; 29,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,17; 28,4</t>
+          <t>20,86; 28,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48,0; 55,43</t>
+          <t>48,09; 55,47</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38,76; 47,39</t>
+          <t>38,99; 47,14</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,65; 30,34</t>
+          <t>23,68; 31,28</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,42; 24,82</t>
+          <t>19,53; 24,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51,25; 57,89</t>
+          <t>51,41; 57,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,21; 42,85</t>
+          <t>35,78; 42,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,01; 28,57</t>
+          <t>23,33; 30,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,69; 29,75</t>
+          <t>22,62; 29,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,2; 64,79</t>
+          <t>57,02; 64,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,69; 57,33</t>
+          <t>49,67; 57,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,17; 72,47</t>
+          <t>20,66; 26,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,55; 25,58</t>
+          <t>21,52; 25,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54,63; 59,77</t>
+          <t>54,62; 59,84</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43,28; 48,36</t>
+          <t>43,02; 48,57</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,52; 60,18</t>
+          <t>23,03; 27,6</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,2; 27,15</t>
+          <t>17,38; 27,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>47,04; 57,31</t>
+          <t>46,77; 56,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38,68; 47,97</t>
+          <t>39,02; 47,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,31; 26,03</t>
+          <t>16,97; 25,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,72; 29,91</t>
+          <t>21,93; 29,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,24; 61,27</t>
+          <t>53,1; 60,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,36; 50,2</t>
+          <t>42,35; 49,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,32; 31,2</t>
+          <t>28,92; 34,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,67; 27,81</t>
+          <t>21,28; 27,74</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51,95; 58,13</t>
+          <t>52,18; 58,13</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41,91; 48,01</t>
+          <t>41,93; 48,04</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,25; 27,85</t>
+          <t>25,26; 30,19</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>32,9%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,26; 23,8</t>
+          <t>11,05; 23,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>39,04; 55,2</t>
+          <t>39,04; 55,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30,39; 45,78</t>
+          <t>29,29; 45,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,39; 31,17</t>
+          <t>13,55; 37,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21,95; 27,31</t>
+          <t>22,18; 27,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>40,74; 47,8</t>
+          <t>41,18; 47,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34,96; 41,58</t>
+          <t>34,95; 41,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30,22; 37,04</t>
+          <t>31,23; 37,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21,46; 26,27</t>
+          <t>21,43; 26,35</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>41,63; 47,68</t>
+          <t>41,56; 47,41</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>35,06; 41,62</t>
+          <t>34,91; 41,37</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>28,16; 34,93</t>
+          <t>29,48; 36,22</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>20,37; 23,69</t>
+          <t>20,17; 23,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>50,14; 53,92</t>
+          <t>49,84; 53,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39,74; 43,78</t>
+          <t>39,65; 43,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21,03; 24,48</t>
+          <t>22,15; 25,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,53; 27,84</t>
+          <t>24,55; 27,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,23; 55,96</t>
+          <t>52,41; 56,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,02; 48,77</t>
+          <t>44,95; 48,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25,74; 47,79</t>
+          <t>26,53; 29,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>23,0; 25,32</t>
+          <t>23,05; 25,37</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51,8; 54,41</t>
+          <t>51,66; 54,3</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43,09; 45,91</t>
+          <t>43,2; 45,9</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>24,25; 39,98</t>
+          <t>24,9; 27,27</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66316</t>
+          <t>75885</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>72164</t>
+          <t>80001</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>138480</t>
+          <t>155886</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>63776; 97276</t>
+          <t>64950; 98342</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>148859; 189246</t>
+          <t>151777; 189492</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>103162; 136601</t>
+          <t>101979; 137705</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50967; 82371</t>
+          <t>60141; 92552</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>55033; 82627</t>
+          <t>53732; 81021</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>134189; 167372</t>
+          <t>132432; 167799</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>122826; 157272</t>
+          <t>124419; 158999</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>60655; 86884</t>
+          <t>66884; 95123</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>127833; 172274</t>
+          <t>126154; 169815</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>293661; 346494</t>
+          <t>297483; 346915</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>236532; 283141</t>
+          <t>235916; 284460</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>119765; 158678</t>
+          <t>135417; 180060</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>57934</t>
+          <t>64743</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>67801</t>
+          <t>76576</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>125735</t>
+          <t>141319</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>44951; 72910</t>
+          <t>45830; 75215</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>154431; 194850</t>
+          <t>152941; 191962</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>115170; 148135</t>
+          <t>112873; 148462</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>44690; 71837</t>
+          <t>51084; 81119</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>73771; 105064</t>
+          <t>74177; 104895</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>170332; 204737</t>
+          <t>171326; 206640</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>152993; 188082</t>
+          <t>153720; 188057</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>57170; 78604</t>
+          <t>64559; 90688</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>127788; 171427</t>
+          <t>126099; 167397</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>336073; 393241</t>
+          <t>335824; 389847</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>279614; 326584</t>
+          <t>279966; 329626</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>109620; 144994</t>
+          <t>122270; 162108</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84893</t>
+          <t>97519</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32141</t>
+          <t>35764</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>117034</t>
+          <t>133284</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>83188; 119043</t>
+          <t>81249; 116776</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>245288; 289570</t>
+          <t>244956; 292387</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>160606; 201101</t>
+          <t>160919; 202351</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>69586; 98440</t>
+          <t>82133; 115750</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>33252; 55710</t>
+          <t>32395; 56100</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>109629; 141444</t>
+          <t>109276; 141385</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>53510; 79169</t>
+          <t>51744; 77925</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25095; 40643</t>
+          <t>27474; 44094</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>123946; 166303</t>
+          <t>122159; 164728</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>364105; 420530</t>
+          <t>364826; 420770</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>221776; 271149</t>
+          <t>223111; 269721</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>100554; 134654</t>
+          <t>117953; 155845</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>178451</t>
+          <t>207177</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>339604</t>
+          <t>153211</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>518055</t>
+          <t>360388</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>190993; 244084</t>
+          <t>192033; 241512</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>492421; 556242</t>
+          <t>493974; 555137</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>316048; 374043</t>
+          <t>312310; 372831</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>155781; 202139</t>
+          <t>181942; 234443</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>136457; 178936</t>
+          <t>136054; 178816</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>376863; 426904</t>
+          <t>375670; 428075</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>325993; 376115</t>
+          <t>325866; 378668</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>175271; 573029</t>
+          <t>135177; 171607</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>341532; 405412</t>
+          <t>341006; 404338</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>884887; 968168</t>
+          <t>884785; 969289</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>661752; 739404</t>
+          <t>657765; 742587</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>352371; 901720</t>
+          <t>330259; 395867</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>72241</t>
+          <t>81612</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>185039</t>
+          <t>213869</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>257280</t>
+          <t>295482</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>46295; 73063</t>
+          <t>46774; 74621</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>194853; 237400</t>
+          <t>193749; 234387</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>185922; 230612</t>
+          <t>187570; 229837</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>59315; 89189</t>
+          <t>65973; 100286</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>109033; 150163</t>
+          <t>110129; 149623</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>374349; 430794</t>
+          <t>373345; 426966</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>279367; 331095</t>
+          <t>279270; 328364</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>136563; 220542</t>
+          <t>196513; 235713</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>167099; 214448</t>
+          <t>164141; 213940</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>580451; 649567</t>
+          <t>583060; 649541</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>477833; 547412</t>
+          <t>478037; 547771</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>191508; 292266</t>
+          <t>269825; 322433</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18094</t>
+          <t>24435</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>196985</t>
+          <t>223683</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>215079</t>
+          <t>248119</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16343; 34548</t>
+          <t>16035; 34583</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>59881; 84663</t>
+          <t>59881; 84882</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45684; 68812</t>
+          <t>44030; 68617</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9989; 33177</t>
+          <t>13953; 38682</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>235561; 292995</t>
+          <t>237942; 294482</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>397350; 466279</t>
+          <t>401683; 465360</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>314456; 373982</t>
+          <t>314347; 373417</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>176264; 215990</t>
+          <t>203347; 246826</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>261349; 319948</t>
+          <t>261043; 320925</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>469916; 538239</t>
+          <t>469121; 535211</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>368014; 436927</t>
+          <t>366537; 434285</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>194168; 240897</t>
+          <t>222261; 273085</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>477929</t>
+          <t>551372</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>893734</t>
+          <t>783104</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1371663</t>
+          <t>1334476</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>501252; 583018</t>
+          <t>496330; 581088</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1375936; 1479626</t>
+          <t>1367767; 1474639</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>992598; 1093651</t>
+          <t>990293; 1094127</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>443163; 515755</t>
+          <t>511313; 592681</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>704477; 799555</t>
+          <t>705289; 803277</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1637716; 1754669</t>
+          <t>1643371; 1757053</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1324977; 1435480</t>
+          <t>1322793; 1437496</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>725908; 1347730</t>
+          <t>744021; 828856</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1226400; 1350393</t>
+          <t>1229267; 1352926</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3045600; 3199012</t>
+          <t>3037623; 3192617</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2344664; 2497812</t>
+          <t>2350654; 2497367</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1194835; 1969747</t>
+          <t>1273159; 1394291</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2B_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2B_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 99,95%)</t>
+          <t>Población que convive con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 99,95%)</t>
+          <t>Población que convive con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
